--- a/계시 환산.xlsx
+++ b/계시 환산.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gustj\Documents\GitHub\dnf-hell-optimizer-react\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A63FCD4B-9D4B-4FF4-BC43-85410FAD2242}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2520BC0-78D7-4960-928E-6658BAFC8EFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1860" yWindow="1860" windowWidth="21600" windowHeight="11295" xr2:uid="{769C35A8-E493-4706-B4D4-CD4E84340BA2}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{769C35A8-E493-4706-B4D4-CD4E84340BA2}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="81">
   <si>
     <t>레어</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -310,6 +310,22 @@
   </si>
   <si>
     <t>판수</t>
+  </si>
+  <si>
+    <t>아포칼립스 3단계</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>미카엘라 매칭</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>미카엘라 일반</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>미카엘라 하드</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -735,7 +751,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{964CAE93-EE7B-4DFE-95DC-363F663B2163}">
-  <dimension ref="A1:L41"/>
+  <dimension ref="A1:L42"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="26.25" bestFit="1" customWidth="1"/>
@@ -1169,583 +1185,583 @@
         <v>70</v>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A22" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B22" s="6">
-        <f>Sheet3!$B2*Sheet1!B$2</f>
-        <v>3</v>
-      </c>
-      <c r="C22" s="6">
-        <f>Sheet3!$B2*Sheet1!C$2</f>
-        <v>2.4000000000000004</v>
-      </c>
-      <c r="D22" s="6">
-        <f>Sheet3!$B2*Sheet1!D$2</f>
-        <v>0.43199999999999994</v>
-      </c>
-      <c r="E22" s="6">
-        <f>Sheet3!$B2*Sheet1!E$2</f>
-        <v>0.192</v>
-      </c>
-      <c r="F22" s="6">
-        <f>Sheet3!$B2*Sheet1!F$2</f>
-        <v>1.992E-2</v>
-      </c>
-      <c r="G22" s="6">
-        <f>Sheet3!$C2*SUM($B$9:$F$9)/4</f>
-        <v>27.709999999999997</v>
-      </c>
-    </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A23" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B23" s="6">
-        <f>Sheet3!$B3*Sheet1!B$2</f>
+        <f>Sheet3!$B6*Sheet1!B$2</f>
         <v>3</v>
       </c>
       <c r="C23" s="6">
-        <f>Sheet3!$B3*Sheet1!C$2</f>
+        <f>Sheet3!$B6*Sheet1!C$2</f>
         <v>2.4000000000000004</v>
       </c>
       <c r="D23" s="6">
-        <f>Sheet3!$B3*Sheet1!D$2</f>
+        <f>Sheet3!$B6*Sheet1!D$2</f>
         <v>0.43199999999999994</v>
       </c>
       <c r="E23" s="6">
-        <f>Sheet3!$B3*Sheet1!E$2</f>
+        <f>Sheet3!$B6*Sheet1!E$2</f>
         <v>0.192</v>
       </c>
       <c r="F23" s="6">
-        <f>Sheet3!$B3*Sheet1!F$2</f>
+        <f>Sheet3!$B6*Sheet1!F$2</f>
         <v>1.992E-2</v>
       </c>
       <c r="G23" s="6">
-        <f>Sheet3!$C3*SUM($B$9:$F$9)/4</f>
-        <v>22.82</v>
+        <f>Sheet3!$C6*SUM($B$9:$F$9)/4</f>
+        <v>27.709999999999997</v>
       </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A24" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B24" s="6">
-        <f>Sheet3!$B4*Sheet1!B$2</f>
+        <f>Sheet3!$B7*Sheet1!B$2</f>
         <v>3</v>
       </c>
       <c r="C24" s="6">
-        <f>Sheet3!$B4*Sheet1!C$2</f>
+        <f>Sheet3!$B7*Sheet1!C$2</f>
         <v>2.4000000000000004</v>
       </c>
       <c r="D24" s="6">
-        <f>Sheet3!$B4*Sheet1!D$2</f>
+        <f>Sheet3!$B7*Sheet1!D$2</f>
         <v>0.43199999999999994</v>
       </c>
       <c r="E24" s="6">
-        <f>Sheet3!$B4*Sheet1!E$2</f>
+        <f>Sheet3!$B7*Sheet1!E$2</f>
         <v>0.192</v>
       </c>
       <c r="F24" s="6">
-        <f>Sheet3!$B4*Sheet1!F$2</f>
+        <f>Sheet3!$B7*Sheet1!F$2</f>
         <v>1.992E-2</v>
       </c>
       <c r="G24" s="6">
-        <f>Sheet3!$C4*SUM($B$9:$F$9)/4</f>
-        <v>14.669999999999998</v>
+        <f>Sheet3!$C7*SUM($B$9:$F$9)/4</f>
+        <v>22.82</v>
       </c>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A25" s="3" t="s">
-        <v>31</v>
+        <v>43</v>
       </c>
       <c r="B25" s="6">
-        <f>Sheet3!$B5*Sheet1!B$2</f>
+        <f>Sheet3!$B8*Sheet1!B$2</f>
         <v>3</v>
       </c>
       <c r="C25" s="6">
-        <f>Sheet3!$B5*Sheet1!C$2</f>
+        <f>Sheet3!$B8*Sheet1!C$2</f>
         <v>2.4000000000000004</v>
       </c>
       <c r="D25" s="6">
-        <f>Sheet3!$B5*Sheet1!D$2</f>
+        <f>Sheet3!$B8*Sheet1!D$2</f>
         <v>0.43199999999999994</v>
       </c>
       <c r="E25" s="6">
-        <f>Sheet3!$B5*Sheet1!E$2</f>
+        <f>Sheet3!$B8*Sheet1!E$2</f>
         <v>0.192</v>
       </c>
       <c r="F25" s="6">
-        <f>Sheet3!$B5*Sheet1!F$2</f>
+        <f>Sheet3!$B8*Sheet1!F$2</f>
         <v>1.992E-2</v>
       </c>
       <c r="G25" s="6">
-        <f>Sheet3!$C5*SUM($B$9:$F$9)/4</f>
-        <v>24.45</v>
+        <f>Sheet3!$C8*SUM($B$9:$F$9)/4</f>
+        <v>14.669999999999998</v>
       </c>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A26" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B26" s="6">
-        <f>Sheet3!$B6*Sheet1!B$2</f>
+        <f>Sheet3!$B9*Sheet1!B$2</f>
         <v>3</v>
       </c>
       <c r="C26" s="6">
-        <f>Sheet3!$B6*Sheet1!C$2</f>
+        <f>Sheet3!$B9*Sheet1!C$2</f>
         <v>2.4000000000000004</v>
       </c>
       <c r="D26" s="6">
-        <f>Sheet3!$B6*Sheet1!D$2</f>
+        <f>Sheet3!$B9*Sheet1!D$2</f>
         <v>0.43199999999999994</v>
       </c>
       <c r="E26" s="6">
-        <f>Sheet3!$B6*Sheet1!E$2</f>
+        <f>Sheet3!$B9*Sheet1!E$2</f>
         <v>0.192</v>
       </c>
       <c r="F26" s="6">
-        <f>Sheet3!$B6*Sheet1!F$2</f>
+        <f>Sheet3!$B9*Sheet1!F$2</f>
         <v>1.992E-2</v>
       </c>
       <c r="G26" s="6">
-        <f>Sheet3!$C6*SUM($B$9:$F$9)/4</f>
-        <v>19.559999999999999</v>
+        <f>Sheet3!$C9*SUM($B$9:$F$9)/4</f>
+        <v>24.45</v>
       </c>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A27" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B27" s="6">
-        <f>Sheet3!$B7*Sheet1!B$2</f>
+        <f>Sheet3!$B10*Sheet1!B$2</f>
         <v>3</v>
       </c>
       <c r="C27" s="6">
-        <f>Sheet3!$B7*Sheet1!C$2</f>
+        <f>Sheet3!$B10*Sheet1!C$2</f>
         <v>2.4000000000000004</v>
       </c>
       <c r="D27" s="6">
-        <f>Sheet3!$B7*Sheet1!D$2</f>
+        <f>Sheet3!$B10*Sheet1!D$2</f>
         <v>0.43199999999999994</v>
       </c>
       <c r="E27" s="6">
-        <f>Sheet3!$B7*Sheet1!E$2</f>
+        <f>Sheet3!$B10*Sheet1!E$2</f>
         <v>0.192</v>
       </c>
       <c r="F27" s="6">
-        <f>Sheet3!$B7*Sheet1!F$2</f>
+        <f>Sheet3!$B10*Sheet1!F$2</f>
         <v>1.992E-2</v>
       </c>
       <c r="G27" s="6">
-        <f>Sheet3!$C7*SUM($B$9:$F$9)/4</f>
-        <v>14.669999999999998</v>
+        <f>Sheet3!$C10*SUM($B$9:$F$9)/4</f>
+        <v>19.559999999999999</v>
       </c>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A28" s="3" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B28" s="6">
-        <f>Sheet3!$B8*Sheet1!B$2</f>
-        <v>2.75</v>
+        <f>Sheet3!$B11*Sheet1!B$2</f>
+        <v>3</v>
       </c>
       <c r="C28" s="6">
-        <f>Sheet3!$B8*Sheet1!C$2</f>
-        <v>2.2000000000000002</v>
+        <f>Sheet3!$B11*Sheet1!C$2</f>
+        <v>2.4000000000000004</v>
       </c>
       <c r="D28" s="6">
-        <f>Sheet3!$B8*Sheet1!D$2</f>
-        <v>0.39599999999999996</v>
+        <f>Sheet3!$B11*Sheet1!D$2</f>
+        <v>0.43199999999999994</v>
       </c>
       <c r="E28" s="6">
-        <f>Sheet3!$B8*Sheet1!E$2</f>
-        <v>0.17599999999999999</v>
+        <f>Sheet3!$B11*Sheet1!E$2</f>
+        <v>0.192</v>
       </c>
       <c r="F28" s="6">
-        <f>Sheet3!$B8*Sheet1!F$2</f>
-        <v>1.8259999999999998E-2</v>
+        <f>Sheet3!$B11*Sheet1!F$2</f>
+        <v>1.992E-2</v>
       </c>
       <c r="G28" s="6">
-        <f>Sheet3!$C8*SUM($B$9:$F$9)/4</f>
-        <v>11.41</v>
+        <f>Sheet3!$C11*SUM($B$9:$F$9)/4</f>
+        <v>14.669999999999998</v>
       </c>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A29" s="3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B29" s="6">
-        <f>Sheet3!$B9*Sheet1!B$2</f>
-        <v>2.5</v>
+        <f>Sheet3!$B12*Sheet1!B$2</f>
+        <v>2.75</v>
       </c>
       <c r="C29" s="6">
-        <f>Sheet3!$B9*Sheet1!C$2</f>
-        <v>2</v>
+        <f>Sheet3!$B12*Sheet1!C$2</f>
+        <v>2.2000000000000002</v>
       </c>
       <c r="D29" s="6">
-        <f>Sheet3!$B9*Sheet1!D$2</f>
-        <v>0.36</v>
+        <f>Sheet3!$B12*Sheet1!D$2</f>
+        <v>0.39599999999999996</v>
       </c>
       <c r="E29" s="6">
-        <f>Sheet3!$B9*Sheet1!E$2</f>
-        <v>0.16</v>
+        <f>Sheet3!$B12*Sheet1!E$2</f>
+        <v>0.17599999999999999</v>
       </c>
       <c r="F29" s="6">
-        <f>Sheet3!$B9*Sheet1!F$2</f>
-        <v>1.66E-2</v>
+        <f>Sheet3!$B12*Sheet1!F$2</f>
+        <v>1.8259999999999998E-2</v>
       </c>
       <c r="G29" s="6">
-        <f>Sheet3!$C9*SUM($B$9:$F$9)/4</f>
-        <v>6.52</v>
+        <f>Sheet3!$C12*SUM($B$9:$F$9)/4</f>
+        <v>11.41</v>
       </c>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A30" s="3" t="s">
-        <v>46</v>
+        <v>35</v>
       </c>
       <c r="B30" s="6">
-        <f>Sheet3!$B10*Sheet1!B$2</f>
-        <v>1.75</v>
+        <f>Sheet3!$B13*Sheet1!B$2</f>
+        <v>2.5</v>
       </c>
       <c r="C30" s="6">
-        <f>Sheet3!$B10*Sheet1!C$2</f>
-        <v>1.4000000000000001</v>
+        <f>Sheet3!$B13*Sheet1!C$2</f>
+        <v>2</v>
       </c>
       <c r="D30" s="6">
-        <f>Sheet3!$B10*Sheet1!D$2</f>
-        <v>0.252</v>
+        <f>Sheet3!$B13*Sheet1!D$2</f>
+        <v>0.36</v>
       </c>
       <c r="E30" s="6">
-        <f>Sheet3!$B10*Sheet1!E$2</f>
-        <v>0.112</v>
+        <f>Sheet3!$B13*Sheet1!E$2</f>
+        <v>0.16</v>
       </c>
       <c r="F30" s="6">
-        <f>Sheet3!$B10*Sheet1!F$2</f>
-        <v>1.162E-2</v>
+        <f>Sheet3!$B13*Sheet1!F$2</f>
+        <v>1.66E-2</v>
       </c>
       <c r="G30" s="6">
-        <f>Sheet3!$C10*SUM($B$9:$F$9)/4</f>
-        <v>4.8899999999999997</v>
+        <f>Sheet3!$C13*SUM($B$9:$F$9)/4</f>
+        <v>6.52</v>
       </c>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A31" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B31" s="6">
-        <f>Sheet3!$B11*Sheet1!B$2</f>
-        <v>3</v>
+        <f>Sheet3!$B14*Sheet1!B$2</f>
+        <v>1.75</v>
       </c>
       <c r="C31" s="6">
-        <f>Sheet3!$B11*Sheet1!C$2</f>
-        <v>2.4000000000000004</v>
+        <f>Sheet3!$B14*Sheet1!C$2</f>
+        <v>1.4000000000000001</v>
       </c>
       <c r="D31" s="6">
-        <f>Sheet3!$B11*Sheet1!D$2</f>
-        <v>0.43199999999999994</v>
+        <f>Sheet3!$B14*Sheet1!D$2</f>
+        <v>0.252</v>
       </c>
       <c r="E31" s="6">
-        <f>Sheet3!$B11*Sheet1!E$2</f>
-        <v>0.192</v>
+        <f>Sheet3!$B14*Sheet1!E$2</f>
+        <v>0.112</v>
       </c>
       <c r="F31" s="6">
-        <f>Sheet3!$B11*Sheet1!F$2</f>
-        <v>1.992E-2</v>
+        <f>Sheet3!$B14*Sheet1!F$2</f>
+        <v>1.162E-2</v>
       </c>
       <c r="G31" s="6">
-        <f>Sheet3!$C11*SUM($B$9:$F$9)/4</f>
-        <v>16.299999999999997</v>
+        <f>Sheet3!$C14*SUM($B$9:$F$9)/4</f>
+        <v>4.8899999999999997</v>
       </c>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A32" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B32" s="6">
-        <f>Sheet3!$B12*Sheet1!B$2</f>
+        <f>Sheet3!$B15*Sheet1!B$2</f>
         <v>3</v>
       </c>
       <c r="C32" s="6">
-        <f>Sheet3!$B12*Sheet1!C$2</f>
+        <f>Sheet3!$B15*Sheet1!C$2</f>
         <v>2.4000000000000004</v>
       </c>
       <c r="D32" s="6">
-        <f>Sheet3!$B12*Sheet1!D$2</f>
+        <f>Sheet3!$B15*Sheet1!D$2</f>
         <v>0.43199999999999994</v>
       </c>
       <c r="E32" s="6">
-        <f>Sheet3!$B12*Sheet1!E$2</f>
+        <f>Sheet3!$B15*Sheet1!E$2</f>
         <v>0.192</v>
       </c>
       <c r="F32" s="6">
-        <f>Sheet3!$B12*Sheet1!F$2</f>
+        <f>Sheet3!$B15*Sheet1!F$2</f>
         <v>1.992E-2</v>
       </c>
       <c r="G32" s="6">
-        <f>Sheet3!$C12*SUM($B$9:$F$9)/4</f>
-        <v>14.669999999999998</v>
+        <f>Sheet3!$C15*SUM($B$9:$F$9)/4</f>
+        <v>16.299999999999997</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A33" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B33" s="6">
-        <f>Sheet3!$B13*Sheet1!B$2</f>
-        <v>2.5</v>
+        <f>Sheet3!$B16*Sheet1!B$2</f>
+        <v>3</v>
       </c>
       <c r="C33" s="6">
-        <f>Sheet3!$B13*Sheet1!C$2</f>
-        <v>2</v>
+        <f>Sheet3!$B16*Sheet1!C$2</f>
+        <v>2.4000000000000004</v>
       </c>
       <c r="D33" s="6">
-        <f>Sheet3!$B13*Sheet1!D$2</f>
-        <v>0.36</v>
+        <f>Sheet3!$B16*Sheet1!D$2</f>
+        <v>0.43199999999999994</v>
       </c>
       <c r="E33" s="6">
-        <f>Sheet3!$B13*Sheet1!E$2</f>
-        <v>0.16</v>
+        <f>Sheet3!$B16*Sheet1!E$2</f>
+        <v>0.192</v>
       </c>
       <c r="F33" s="6">
-        <f>Sheet3!$B13*Sheet1!F$2</f>
-        <v>1.66E-2</v>
+        <f>Sheet3!$B16*Sheet1!F$2</f>
+        <v>1.992E-2</v>
       </c>
       <c r="G33" s="6">
-        <f>Sheet3!$C13*SUM($B$9:$F$9)/4</f>
-        <v>9.7799999999999994</v>
+        <f>Sheet3!$C16*SUM($B$9:$F$9)/4</f>
+        <v>14.669999999999998</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A34" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B34" s="6">
-        <f>Sheet3!$B14*Sheet1!B$2</f>
-        <v>2.25</v>
+        <f>Sheet3!$B17*Sheet1!B$2</f>
+        <v>2.5</v>
       </c>
       <c r="C34" s="6">
-        <f>Sheet3!$B14*Sheet1!C$2</f>
-        <v>1.8</v>
+        <f>Sheet3!$B17*Sheet1!C$2</f>
+        <v>2</v>
       </c>
       <c r="D34" s="6">
-        <f>Sheet3!$B14*Sheet1!D$2</f>
-        <v>0.32399999999999995</v>
+        <f>Sheet3!$B17*Sheet1!D$2</f>
+        <v>0.36</v>
       </c>
       <c r="E34" s="6">
-        <f>Sheet3!$B14*Sheet1!E$2</f>
-        <v>0.14400000000000002</v>
+        <f>Sheet3!$B17*Sheet1!E$2</f>
+        <v>0.16</v>
       </c>
       <c r="F34" s="6">
-        <f>Sheet3!$B14*Sheet1!F$2</f>
-        <v>1.494E-2</v>
+        <f>Sheet3!$B17*Sheet1!F$2</f>
+        <v>1.66E-2</v>
       </c>
       <c r="G34" s="6">
-        <f>Sheet3!$C14*SUM($B$9:$F$9)/4</f>
-        <v>8.1499999999999986</v>
+        <f>Sheet3!$C17*SUM($B$9:$F$9)/4</f>
+        <v>9.7799999999999994</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A35" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B35" s="6">
-        <f>Sheet3!$B15*Sheet1!B$2</f>
-        <v>3</v>
+        <f>Sheet3!$B18*Sheet1!B$2</f>
+        <v>2.25</v>
       </c>
       <c r="C35" s="6">
-        <f>Sheet3!$B15*Sheet1!C$2</f>
-        <v>2.4000000000000004</v>
+        <f>Sheet3!$B18*Sheet1!C$2</f>
+        <v>1.8</v>
       </c>
       <c r="D35" s="6">
-        <f>Sheet3!$B15*Sheet1!D$2</f>
-        <v>0.43199999999999994</v>
+        <f>Sheet3!$B18*Sheet1!D$2</f>
+        <v>0.32399999999999995</v>
       </c>
       <c r="E35" s="6">
-        <f>Sheet3!$B15*Sheet1!E$2</f>
-        <v>0.192</v>
+        <f>Sheet3!$B18*Sheet1!E$2</f>
+        <v>0.14400000000000002</v>
       </c>
       <c r="F35" s="6">
-        <f>Sheet3!$B15*Sheet1!F$2</f>
-        <v>1.992E-2</v>
+        <f>Sheet3!$B18*Sheet1!F$2</f>
+        <v>1.494E-2</v>
       </c>
       <c r="G35" s="6">
-        <f>Sheet3!$C15*SUM($B$9:$F$9)/4</f>
-        <v>0</v>
+        <f>Sheet3!$C18*SUM($B$9:$F$9)/4</f>
+        <v>8.1499999999999986</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A36" s="3" t="s">
-        <v>36</v>
+        <v>51</v>
       </c>
       <c r="B36" s="6">
-        <f>Sheet3!$B16*Sheet1!B$2</f>
+        <f>Sheet3!$B19*Sheet1!B$2</f>
         <v>3</v>
       </c>
       <c r="C36" s="6">
-        <f>Sheet3!$B16*Sheet1!C$2</f>
+        <f>Sheet3!$B19*Sheet1!C$2</f>
         <v>2.4000000000000004</v>
       </c>
       <c r="D36" s="6">
-        <f>Sheet3!$B16*Sheet1!D$2</f>
+        <f>Sheet3!$B19*Sheet1!D$2</f>
         <v>0.43199999999999994</v>
       </c>
       <c r="E36" s="6">
-        <f>Sheet3!$B16*Sheet1!E$2</f>
+        <f>Sheet3!$B19*Sheet1!E$2</f>
         <v>0.192</v>
       </c>
       <c r="F36" s="6">
-        <f>Sheet3!$B16*Sheet1!F$2</f>
+        <f>Sheet3!$B19*Sheet1!F$2</f>
         <v>1.992E-2</v>
       </c>
       <c r="G36" s="6">
-        <f>Sheet3!$C16*SUM($B$9:$F$9)/4</f>
+        <f>Sheet3!$C19*SUM($B$9:$F$9)/4</f>
         <v>0</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A37" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B37" s="6">
-        <f>Sheet3!$B17*Sheet1!B$2</f>
-        <v>2</v>
+        <f>Sheet3!$B20*Sheet1!B$2</f>
+        <v>3</v>
       </c>
       <c r="C37" s="6">
-        <f>Sheet3!$B17*Sheet1!C$2</f>
-        <v>1.6</v>
+        <f>Sheet3!$B20*Sheet1!C$2</f>
+        <v>2.4000000000000004</v>
       </c>
       <c r="D37" s="6">
-        <f>Sheet3!$B17*Sheet1!D$2</f>
-        <v>0.28799999999999998</v>
+        <f>Sheet3!$B20*Sheet1!D$2</f>
+        <v>0.43199999999999994</v>
       </c>
       <c r="E37" s="6">
-        <f>Sheet3!$B17*Sheet1!E$2</f>
-        <v>0.128</v>
+        <f>Sheet3!$B20*Sheet1!E$2</f>
+        <v>0.192</v>
       </c>
       <c r="F37" s="6">
-        <f>Sheet3!$B17*Sheet1!F$2</f>
-        <v>1.328E-2</v>
+        <f>Sheet3!$B20*Sheet1!F$2</f>
+        <v>1.992E-2</v>
       </c>
       <c r="G37" s="6">
-        <f>Sheet3!$C17*SUM($B$9:$F$9)/4</f>
+        <f>Sheet3!$C20*SUM($B$9:$F$9)/4</f>
         <v>0</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A38" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B38" s="6">
-        <f>Sheet3!$B18*Sheet1!B$2</f>
-        <v>1.75</v>
+        <f>Sheet3!$B21*Sheet1!B$2</f>
+        <v>2</v>
       </c>
       <c r="C38" s="6">
-        <f>Sheet3!$B18*Sheet1!C$2</f>
-        <v>1.4000000000000001</v>
+        <f>Sheet3!$B21*Sheet1!C$2</f>
+        <v>1.6</v>
       </c>
       <c r="D38" s="6">
-        <f>Sheet3!$B18*Sheet1!D$2</f>
-        <v>0.252</v>
+        <f>Sheet3!$B21*Sheet1!D$2</f>
+        <v>0.28799999999999998</v>
       </c>
       <c r="E38" s="6">
-        <f>Sheet3!$B18*Sheet1!E$2</f>
-        <v>0.112</v>
+        <f>Sheet3!$B21*Sheet1!E$2</f>
+        <v>0.128</v>
       </c>
       <c r="F38" s="6">
-        <f>Sheet3!$B18*Sheet1!F$2</f>
-        <v>1.162E-2</v>
+        <f>Sheet3!$B21*Sheet1!F$2</f>
+        <v>1.328E-2</v>
       </c>
       <c r="G38" s="6">
-        <f>Sheet3!$C18*SUM($B$9:$F$9)/4</f>
+        <f>Sheet3!$C21*SUM($B$9:$F$9)/4</f>
         <v>0</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A39" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B39" s="6">
-        <f>Sheet3!$B19*Sheet1!B$2</f>
-        <v>2</v>
+        <f>Sheet3!$B22*Sheet1!B$2</f>
+        <v>1.75</v>
       </c>
       <c r="C39" s="6">
-        <f>Sheet3!$B19*Sheet1!C$2</f>
-        <v>1.6</v>
+        <f>Sheet3!$B22*Sheet1!C$2</f>
+        <v>1.4000000000000001</v>
       </c>
       <c r="D39" s="6">
-        <f>Sheet3!$B19*Sheet1!D$2</f>
-        <v>0.28799999999999998</v>
+        <f>Sheet3!$B22*Sheet1!D$2</f>
+        <v>0.252</v>
       </c>
       <c r="E39" s="6">
-        <f>Sheet3!$B19*Sheet1!E$2</f>
-        <v>0.128</v>
+        <f>Sheet3!$B22*Sheet1!E$2</f>
+        <v>0.112</v>
       </c>
       <c r="F39" s="6">
-        <f>Sheet3!$B19*Sheet1!F$2</f>
-        <v>1.328E-2</v>
+        <f>Sheet3!$B22*Sheet1!F$2</f>
+        <v>1.162E-2</v>
       </c>
       <c r="G39" s="6">
-        <f>Sheet3!$C19*SUM($B$9:$F$9)/4</f>
+        <f>Sheet3!$C22*SUM($B$9:$F$9)/4</f>
         <v>0</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A40" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B40" s="6">
-        <f>Sheet3!$B20*Sheet1!B$2</f>
-        <v>1.25</v>
+        <f>Sheet3!$B23*Sheet1!B$2</f>
+        <v>2</v>
       </c>
       <c r="C40" s="6">
-        <f>Sheet3!$B20*Sheet1!C$2</f>
-        <v>1</v>
+        <f>Sheet3!$B23*Sheet1!C$2</f>
+        <v>1.6</v>
       </c>
       <c r="D40" s="6">
-        <f>Sheet3!$B20*Sheet1!D$2</f>
-        <v>0.18</v>
+        <f>Sheet3!$B23*Sheet1!D$2</f>
+        <v>0.28799999999999998</v>
       </c>
       <c r="E40" s="6">
-        <f>Sheet3!$B20*Sheet1!E$2</f>
-        <v>0.08</v>
+        <f>Sheet3!$B23*Sheet1!E$2</f>
+        <v>0.128</v>
       </c>
       <c r="F40" s="6">
-        <f>Sheet3!$B20*Sheet1!F$2</f>
-        <v>8.3000000000000001E-3</v>
+        <f>Sheet3!$B23*Sheet1!F$2</f>
+        <v>1.328E-2</v>
       </c>
       <c r="G40" s="6">
-        <f>Sheet3!$C20*SUM($B$9:$F$9)/4</f>
+        <f>Sheet3!$C23*SUM($B$9:$F$9)/4</f>
         <v>0</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A41" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B41" s="6">
+        <f>Sheet3!$B24*Sheet1!B$2</f>
+        <v>1.25</v>
+      </c>
+      <c r="C41" s="6">
+        <f>Sheet3!$B24*Sheet1!C$2</f>
+        <v>1</v>
+      </c>
+      <c r="D41" s="6">
+        <f>Sheet3!$B24*Sheet1!D$2</f>
+        <v>0.18</v>
+      </c>
+      <c r="E41" s="6">
+        <f>Sheet3!$B24*Sheet1!E$2</f>
+        <v>0.08</v>
+      </c>
+      <c r="F41" s="6">
+        <f>Sheet3!$B24*Sheet1!F$2</f>
+        <v>8.3000000000000001E-3</v>
+      </c>
+      <c r="G41" s="6">
+        <f>Sheet3!$C24*SUM($B$9:$F$9)/4</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A42" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="B41" s="6">
-        <f>Sheet3!$B21*Sheet1!B$2</f>
+      <c r="B42" s="6">
+        <f>Sheet3!$B25*Sheet1!B$2</f>
         <v>3.5</v>
       </c>
-      <c r="C41" s="6">
-        <f>Sheet3!$B21*Sheet1!C$2</f>
+      <c r="C42" s="6">
+        <f>Sheet3!$B25*Sheet1!C$2</f>
         <v>2.8000000000000003</v>
       </c>
-      <c r="D41" s="6">
-        <f>Sheet3!$B21*Sheet1!D$2</f>
+      <c r="D42" s="6">
+        <f>Sheet3!$B25*Sheet1!D$2</f>
         <v>0.504</v>
       </c>
-      <c r="E41" s="6">
-        <f>Sheet3!$B21*Sheet1!E$2</f>
+      <c r="E42" s="6">
+        <f>Sheet3!$B25*Sheet1!E$2</f>
         <v>0.224</v>
       </c>
-      <c r="F41" s="6">
-        <f>Sheet3!$B21*Sheet1!F$2</f>
+      <c r="F42" s="6">
+        <f>Sheet3!$B25*Sheet1!F$2</f>
         <v>2.324E-2</v>
       </c>
-      <c r="G41" s="6">
-        <f>Sheet3!$C21*SUM($B$9:$F$9)/4</f>
+      <c r="G42" s="6">
+        <f>Sheet3!$C25*SUM($B$9:$F$9)/4</f>
         <v>22.82</v>
       </c>
     </row>
@@ -1756,7 +1772,7 @@
     <mergeCell ref="E18:F18"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="B23:F41 B22">
+  <conditionalFormatting sqref="B24:F42 B23">
     <cfRule type="dataBar" priority="4">
       <dataBar>
         <cfvo type="min"/>
@@ -1770,7 +1786,7 @@
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C22:F22">
+  <conditionalFormatting sqref="C23:F23">
     <cfRule type="dataBar" priority="1">
       <dataBar>
         <cfvo type="min"/>
@@ -1800,7 +1816,7 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>B23:F41 B22</xm:sqref>
+          <xm:sqref>B24:F42 B23</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
           <x14:cfRule type="dataBar" id="{06F48B9D-DE53-4BF8-986C-3096AB01DC74}">
@@ -1813,7 +1829,7 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>C22:F22</xm:sqref>
+          <xm:sqref>C23:F23</xm:sqref>
         </x14:conditionalFormatting>
       </x14:conditionalFormattings>
     </ext>
@@ -2175,7 +2191,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1C59EBE8-B217-4AE7-B116-CA52FA623D3E}">
-  <dimension ref="A1:F21"/>
+  <dimension ref="A1:F25"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="19.25" customWidth="1"/>
@@ -2207,197 +2223,187 @@
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B2" s="3">
+      <c r="A2" t="s">
+        <v>80</v>
+      </c>
+      <c r="B2">
+        <v>15</v>
+      </c>
+      <c r="C2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>79</v>
+      </c>
+      <c r="B3">
+        <v>15</v>
+      </c>
+      <c r="C3">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>78</v>
+      </c>
+      <c r="B4">
         <v>12</v>
       </c>
-      <c r="C2" s="3">
-        <v>17</v>
-      </c>
-      <c r="D2" s="3">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A3" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B3" s="3">
-        <v>12</v>
-      </c>
-      <c r="C3" s="3">
+      <c r="C4">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>77</v>
+      </c>
+      <c r="B5">
         <v>14</v>
       </c>
-      <c r="D3" s="3">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A4" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B4" s="3">
-        <v>12</v>
-      </c>
-      <c r="C4" s="3">
-        <v>9</v>
-      </c>
-      <c r="D4" s="3">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A5" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="B5" s="3">
-        <v>12</v>
-      </c>
-      <c r="C5" s="3">
-        <v>15</v>
-      </c>
-      <c r="D5" s="3">
-        <v>240</v>
+      <c r="C5">
+        <v>21</v>
+      </c>
+      <c r="E5">
+        <v>280</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="B6" s="3">
         <v>12</v>
       </c>
       <c r="C6" s="3">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="D6" s="3">
-        <v>220</v>
+        <v>260</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="B7" s="3">
         <v>12</v>
       </c>
       <c r="C7" s="3">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="D7" s="3">
-        <v>180</v>
+        <v>240</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="B8" s="3">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C8" s="3">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D8" s="3">
-        <v>140</v>
+        <v>180</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" s="3" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="B9" s="3">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C9" s="3">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="D9" s="3">
-        <v>100</v>
+        <v>240</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
-        <v>46</v>
+        <v>32</v>
       </c>
       <c r="B10" s="3">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="C10" s="3">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="D10" s="3">
-        <v>60</v>
+        <v>220</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" s="3" t="s">
-        <v>47</v>
+        <v>33</v>
       </c>
       <c r="B11" s="3">
         <v>12</v>
       </c>
       <c r="C11" s="3">
-        <v>10</v>
-      </c>
-      <c r="D11" s="3"/>
-      <c r="E11" s="3">
+        <v>9</v>
+      </c>
+      <c r="D11" s="3">
         <v>180</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" s="3" t="s">
-        <v>48</v>
+        <v>34</v>
       </c>
       <c r="B12" s="3">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C12" s="3">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D12" s="3">
-        <v>180</v>
+        <v>140</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" s="3" t="s">
-        <v>49</v>
+        <v>35</v>
       </c>
       <c r="B13" s="3">
         <v>10</v>
       </c>
       <c r="C13" s="3">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D13" s="3">
-        <v>160</v>
+        <v>100</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14" s="3" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="B14" s="3">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C14" s="3">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D14" s="3">
-        <v>140</v>
+        <v>60</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15" s="3" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="B15" s="3">
         <v>12</v>
       </c>
       <c r="C15" s="3">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D15" s="3"/>
       <c r="E15" s="3">
@@ -2406,88 +2412,145 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16" s="3" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="B16" s="3">
         <v>12</v>
       </c>
       <c r="C16" s="3">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="D16" s="3">
-        <v>200</v>
+        <v>180</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A17" s="3" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="B17" s="3">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C17" s="3">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D17" s="3">
-        <v>110</v>
+        <v>160</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18" s="3" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="B18" s="3">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C18" s="3">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D18" s="3">
-        <v>90</v>
+        <v>140</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A19" s="3" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="B19" s="3">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="C19" s="3">
         <v>0</v>
       </c>
-      <c r="D19" s="3">
-        <v>100</v>
+      <c r="D19" s="3"/>
+      <c r="E19" s="3">
+        <v>180</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A20" s="3" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="B20" s="3">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="C20" s="3">
         <v>0</v>
       </c>
       <c r="D20" s="3">
-        <v>60</v>
+        <v>200</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A21" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B21" s="3">
+        <v>8</v>
+      </c>
+      <c r="C21" s="3">
+        <v>0</v>
+      </c>
+      <c r="D21" s="3">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A22" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B22" s="3">
+        <v>7</v>
+      </c>
+      <c r="C22" s="3">
+        <v>0</v>
+      </c>
+      <c r="D22" s="3">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A23" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B23" s="3">
+        <v>8</v>
+      </c>
+      <c r="C23" s="3">
+        <v>0</v>
+      </c>
+      <c r="D23" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A24" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B24" s="3">
+        <v>5</v>
+      </c>
+      <c r="C24" s="3">
+        <v>0</v>
+      </c>
+      <c r="D24" s="3">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A25" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="B21" s="3">
+      <c r="B25" s="3">
         <v>14</v>
       </c>
-      <c r="C21" s="3">
+      <c r="C25" s="3">
         <v>14</v>
       </c>
-      <c r="D21">
+      <c r="D25">
         <v>345</v>
       </c>
-      <c r="F21" t="s">
+      <c r="F25" t="s">
         <v>64</v>
       </c>
     </row>
